--- a/Human DM Topics.xlsx
+++ b/Human DM Topics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f1511f0ab29f3824/Documents/behavioral_apps/HUMANS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F248EAA4-24B1-493C-A441-B8C733D76658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{F248EAA4-24B1-493C-A441-B8C733D76658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C9B7D4A-82F1-4554-A9A9-94A7E0F7E6C8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4305" windowWidth="17310" windowHeight="29040" activeTab="1" xr2:uid="{3F1DC614-74A3-41B9-8627-AC851E07792B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{3F1DC614-74A3-41B9-8627-AC851E07792B}"/>
   </bookViews>
   <sheets>
     <sheet name="Topics" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="263">
   <si>
     <t>Approach-Avoid Tasks</t>
   </si>
@@ -1486,6 +1486,60 @@
   </si>
   <si>
     <t>5,7,6</t>
+  </si>
+  <si>
+    <t>Shopping</t>
+  </si>
+  <si>
+    <t>1,2,24,26,38,39,43,6</t>
+  </si>
+  <si>
+    <t>9) Shopping</t>
+  </si>
+  <si>
+    <t>Og-Approach-Avoid</t>
+  </si>
+  <si>
+    <t>Og-Probability</t>
+  </si>
+  <si>
+    <t>10,15,</t>
+  </si>
+  <si>
+    <t>13,16,50,7</t>
+  </si>
+  <si>
+    <t>14,17,21,3,31,4,41,44,47,52,53,56,64,8,9</t>
+  </si>
+  <si>
+    <t>12,18,20,25,27,29,46,55,57,59,60</t>
+  </si>
+  <si>
+    <t>10,15,30,32,33,36,37,61,62</t>
+  </si>
+  <si>
+    <t>19,22</t>
+  </si>
+  <si>
+    <t>12,18,20,25,27</t>
+  </si>
+  <si>
+    <t>19,22,34,35,42,49,63</t>
+  </si>
+  <si>
+    <t>11,28,40,45,48,5,54,58</t>
+  </si>
+  <si>
+    <t>11,28,5</t>
+  </si>
+  <si>
+    <t>1,2,24,26,6</t>
+  </si>
+  <si>
+    <t>13,16,7</t>
+  </si>
+  <si>
+    <t>14,17,21,3,4,8,9</t>
   </si>
 </sst>
 </file>
@@ -1644,10 +1698,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1685,7 +1743,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1791,7 +1849,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1933,7 +1991,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1941,25 +1999,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDBAA15-ED3B-482E-A29B-56C37193E7A6}">
-  <dimension ref="A1:Q30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" customWidth="1"/>
-    <col min="3" max="3" width="45.7109375" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" customWidth="1"/>
-    <col min="5" max="5" width="38.42578125" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" customWidth="1"/>
+    <col min="5" max="5" width="38.44140625" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="36.109375" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" customWidth="1"/>
-    <col min="17" max="17" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="10.88671875" customWidth="1"/>
+    <col min="15" max="15" width="13.109375" customWidth="1"/>
+    <col min="17" max="17" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1988,7 +2046,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -2017,7 +2075,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
@@ -2043,7 +2101,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -2069,7 +2127,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>32</v>
       </c>
@@ -2095,7 +2153,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
@@ -2121,7 +2179,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>48</v>
       </c>
@@ -2147,7 +2205,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
@@ -2173,7 +2231,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>63</v>
       </c>
@@ -2199,7 +2257,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>71</v>
       </c>
@@ -2221,8 +2279,11 @@
       <c r="G10" s="7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>78</v>
       </c>
@@ -2245,7 +2306,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>84</v>
       </c>
@@ -2268,7 +2329,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -2291,7 +2352,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>96</v>
       </c>
@@ -2308,7 +2369,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>101</v>
       </c>
@@ -2331,7 +2392,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>108</v>
       </c>
@@ -2371,8 +2432,11 @@
       <c r="Q16" s="5" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>121</v>
       </c>
@@ -2389,7 +2453,7 @@
         <v>156</v>
       </c>
       <c r="I17" t="s">
-        <v>125</v>
+        <v>248</v>
       </c>
       <c r="J17" t="s">
         <v>157</v>
@@ -2416,7 +2480,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>127</v>
       </c>
@@ -2460,7 +2524,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>133</v>
       </c>
@@ -2504,7 +2568,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>137</v>
       </c>
@@ -2548,7 +2612,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>140</v>
       </c>
@@ -2565,7 +2629,7 @@
         <v>186</v>
       </c>
       <c r="I21" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="J21" t="s">
         <v>219</v>
@@ -2592,7 +2656,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>143</v>
       </c>
@@ -2636,7 +2700,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>146</v>
       </c>
@@ -2680,7 +2744,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>149</v>
       </c>
@@ -2724,7 +2788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>195</v>
       </c>
@@ -2740,16 +2804,70 @@
       <c r="E25" s="8" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I25" t="s">
+        <v>125</v>
+      </c>
+      <c r="J25" t="s">
+        <v>258</v>
+      </c>
+      <c r="K25">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>251</v>
+      </c>
+      <c r="M25" t="s">
+        <v>252</v>
+      </c>
+      <c r="N25" t="s">
+        <v>246</v>
+      </c>
+      <c r="O25" t="s">
+        <v>254</v>
+      </c>
+      <c r="P25" t="s">
+        <v>253</v>
+      </c>
+      <c r="R25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>200</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J26" t="s">
+        <v>259</v>
+      </c>
+      <c r="K26">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>261</v>
+      </c>
+      <c r="M26" t="s">
+        <v>262</v>
+      </c>
+      <c r="N26" t="s">
+        <v>260</v>
+      </c>
+      <c r="O26" t="s">
+        <v>250</v>
+      </c>
+      <c r="P26" t="s">
+        <v>256</v>
+      </c>
+      <c r="R26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
         <v>202</v>
       </c>
@@ -2757,7 +2875,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B28" s="9" t="s">
         <v>204</v>
       </c>
@@ -2765,7 +2883,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
         <v>206</v>
       </c>
@@ -2773,7 +2891,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
         <v>208</v>
       </c>
@@ -2789,10 +2907,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEACEF1-36AE-490C-9533-56233DBF0D5D}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B1" t="str">
         <f>Topics!J16</f>
         <v>Vehicle/Transportation</v>
@@ -2825,11 +2946,15 @@
         <f>Topics!Q16</f>
         <v>Military</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="str">
+        <f>Topics!R16</f>
+        <v>Shopping</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>Topics!I17</f>
-        <v>Approach-Avoid</v>
+        <v>Og-Approach-Avoid</v>
       </c>
       <c r="B2" t="str">
         <f>Topics!J17</f>
@@ -2864,7 +2989,7 @@
         <v>4,11,13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>Topics!I18</f>
         <v>Moral</v>
@@ -2902,7 +3027,7 @@
         <v>11, 16,17,18,19,21,22</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>Topics!I19</f>
         <v>Multi-Choice</v>
@@ -2940,7 +3065,7 @@
         <v>3,4,12,13,14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>Topics!I20</f>
         <v>Social</v>
@@ -2978,10 +3103,10 @@
         <v>1, 15, 16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>Topics!I21</f>
-        <v>Probability</v>
+        <v>Og-Probability</v>
       </c>
       <c r="B6" t="str">
         <f>Topics!J21</f>
@@ -3016,7 +3141,7 @@
         <v>10,11,12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>Topics!I22</f>
         <v>Cost-Cost</v>
@@ -3054,7 +3179,7 @@
         <v>4, 23, 24</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>Topics!I23</f>
         <v>Benefit-Benefit</v>
@@ -3092,7 +3217,7 @@
         <v>1,2, 13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>Topics!I24</f>
         <v>Obvious-Supersense</v>
@@ -3128,6 +3253,90 @@
       <c r="I9">
         <f>Topics!Q24</f>
         <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f>Topics!I25</f>
+        <v>Approach-Avoid</v>
+      </c>
+      <c r="B10" t="str">
+        <f>Topics!J25</f>
+        <v>11,28,40,45,48,5,54,58</v>
+      </c>
+      <c r="C10">
+        <f>Topics!K25</f>
+        <v>23</v>
+      </c>
+      <c r="D10" t="str">
+        <f>Topics!L25</f>
+        <v>13,16,50,7</v>
+      </c>
+      <c r="E10" t="str">
+        <f>Topics!M25</f>
+        <v>14,17,21,3,31,4,41,44,47,52,53,56,64,8,9</v>
+      </c>
+      <c r="F10" t="str">
+        <f>Topics!N25</f>
+        <v>1,2,24,26,38,39,43,6</v>
+      </c>
+      <c r="G10" t="str">
+        <f>Topics!O25</f>
+        <v>10,15,30,32,33,36,37,61,62</v>
+      </c>
+      <c r="H10" t="str">
+        <f>Topics!P25</f>
+        <v>12,18,20,25,27,29,46,55,57,59,60</v>
+      </c>
+      <c r="I10">
+        <f>Topics!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="J10" t="str">
+        <f>Topics!R25</f>
+        <v>19,22,34,35,42,49,63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f>Topics!I26</f>
+        <v>Probability</v>
+      </c>
+      <c r="B11" t="str">
+        <f>Topics!J26</f>
+        <v>11,28,5</v>
+      </c>
+      <c r="C11">
+        <f>Topics!K26</f>
+        <v>23</v>
+      </c>
+      <c r="D11" t="str">
+        <f>Topics!L26</f>
+        <v>13,16,7</v>
+      </c>
+      <c r="E11" t="str">
+        <f>Topics!M26</f>
+        <v>14,17,21,3,4,8,9</v>
+      </c>
+      <c r="F11" t="str">
+        <f>Topics!N26</f>
+        <v>1,2,24,26,6</v>
+      </c>
+      <c r="G11" t="str">
+        <f>Topics!O26</f>
+        <v>10,15,</v>
+      </c>
+      <c r="H11" t="str">
+        <f>Topics!P26</f>
+        <v>12,18,20,25,27</v>
+      </c>
+      <c r="I11">
+        <f>Topics!Q26</f>
+        <v>0</v>
+      </c>
+      <c r="J11" t="str">
+        <f>Topics!R26</f>
+        <v>19,22</v>
       </c>
     </row>
   </sheetData>
